--- a/Datas/TempCharacterData.xlsx
+++ b/Datas/TempCharacterData.xlsx
@@ -7,7 +7,7 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="TempCharacterData" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>

--- a/Datas/TempCharacterData.xlsx
+++ b/Datas/TempCharacterData.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="TempCharacterData" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -19,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="55">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -69,6 +70,134 @@
   </si>
   <si>
     <t>默认消费者</t>
+  </si>
+  <si>
+    <t>匪徒</t>
+  </si>
+  <si>
+    <t>格斗家</t>
+  </si>
+  <si>
+    <t>官员</t>
+  </si>
+  <si>
+    <t>鬼族男</t>
+  </si>
+  <si>
+    <t>贵族骑士</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>老公公</t>
+  </si>
+  <si>
+    <t>老英雄</t>
+  </si>
+  <si>
+    <t>魔族大将</t>
+  </si>
+  <si>
+    <t>魔族法师</t>
+  </si>
+  <si>
+    <t>魔族娃娃</t>
+  </si>
+  <si>
+    <t>女鬼</t>
+  </si>
+  <si>
+    <t>女魔族</t>
+  </si>
+  <si>
+    <t>女轻战士</t>
+  </si>
+  <si>
+    <t>女战士</t>
+  </si>
+  <si>
+    <t>骑士</t>
+  </si>
+  <si>
+    <t>轻战士</t>
+  </si>
+  <si>
+    <t>商人</t>
+  </si>
+  <si>
+    <t>双辫女孩</t>
+  </si>
+  <si>
+    <t>兔女郎</t>
+  </si>
+  <si>
+    <t>武士</t>
+  </si>
+  <si>
+    <t>小孩</t>
+  </si>
+  <si>
+    <t>小花</t>
+  </si>
+  <si>
+    <t>小混混</t>
+  </si>
+  <si>
+    <t>小精灵红</t>
+  </si>
+  <si>
+    <t>小精灵黄</t>
+  </si>
+  <si>
+    <t>小美</t>
+  </si>
+  <si>
+    <t>小男孩</t>
+  </si>
+  <si>
+    <t>小男孩2</t>
+  </si>
+  <si>
+    <t>小女孩</t>
+  </si>
+  <si>
+    <t>小女孩2</t>
+  </si>
+  <si>
+    <t>邪恶法师</t>
+  </si>
+  <si>
+    <t>异国女子</t>
+  </si>
+  <si>
+    <t>勇者男</t>
+  </si>
+  <si>
+    <t>勇者女</t>
+  </si>
+  <si>
+    <t>幽灵战士</t>
+  </si>
+  <si>
+    <t>游侠</t>
+  </si>
+  <si>
+    <t>战斗学者</t>
+  </si>
+  <si>
+    <t>侦探</t>
+  </si>
+  <si>
+    <t>制服小孩</t>
+  </si>
+  <si>
+    <t>重装女战士</t>
+  </si>
+  <si>
+    <t>重装战士</t>
+  </si>
+  <si>
+    <t>街溜子</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -406,7 +535,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:F4"/>
+  <dimension ref="A2:F45"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="3" width="14.125" customWidth="1"/>
@@ -468,9 +597,834 @@
         <v>12</v>
       </c>
     </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>5002</v>
+      </c>
+      <c r="B5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5">
+        <v>68</v>
+      </c>
+      <c r="D5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>5003</v>
+      </c>
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6">
+        <v>51</v>
+      </c>
+      <c r="D6" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>5004</v>
+      </c>
+      <c r="B7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7">
+        <v>62</v>
+      </c>
+      <c r="D7" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>5005</v>
+      </c>
+      <c r="B8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8">
+        <v>45</v>
+      </c>
+      <c r="D8" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>5006</v>
+      </c>
+      <c r="B9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9">
+        <v>47</v>
+      </c>
+      <c r="D9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>5007</v>
+      </c>
+      <c r="B10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10">
+        <v>46</v>
+      </c>
+      <c r="D10" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>5008</v>
+      </c>
+      <c r="B11" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11">
+        <v>63</v>
+      </c>
+      <c r="D11" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>5009</v>
+      </c>
+      <c r="B12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12">
+        <v>65</v>
+      </c>
+      <c r="D12" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>5010</v>
+      </c>
+      <c r="B13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13">
+        <v>41</v>
+      </c>
+      <c r="D13" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>5011</v>
+      </c>
+      <c r="B14" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14">
+        <v>44</v>
+      </c>
+      <c r="D14" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>5012</v>
+      </c>
+      <c r="B15" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15">
+        <v>66</v>
+      </c>
+      <c r="D15" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>5013</v>
+      </c>
+      <c r="B16" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16">
+        <v>67</v>
+      </c>
+      <c r="D16" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>5014</v>
+      </c>
+      <c r="B17" t="s">
+        <v>31</v>
+      </c>
+      <c r="C17">
+        <v>72</v>
+      </c>
+      <c r="D17" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>5015</v>
+      </c>
+      <c r="B18" t="s">
+        <v>32</v>
+      </c>
+      <c r="C18">
+        <v>50</v>
+      </c>
+      <c r="D18" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>5016</v>
+      </c>
+      <c r="B19" t="s">
+        <v>33</v>
+      </c>
+      <c r="C19">
+        <v>59</v>
+      </c>
+      <c r="D19" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>5017</v>
+      </c>
+      <c r="B20" t="s">
+        <v>34</v>
+      </c>
+      <c r="C20">
+        <v>54</v>
+      </c>
+      <c r="D20" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>5018</v>
+      </c>
+      <c r="B21" t="s">
+        <v>35</v>
+      </c>
+      <c r="C21">
+        <v>58</v>
+      </c>
+      <c r="D21" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>5019</v>
+      </c>
+      <c r="B22" t="s">
+        <v>38</v>
+      </c>
+      <c r="C22">
+        <v>55</v>
+      </c>
+      <c r="D22" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>5020</v>
+      </c>
+      <c r="B23" t="s">
+        <v>39</v>
+      </c>
+      <c r="C23">
+        <v>57</v>
+      </c>
+      <c r="D23" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <v>5021</v>
+      </c>
+      <c r="B24" t="s">
+        <v>40</v>
+      </c>
+      <c r="C24">
+        <v>56</v>
+      </c>
+      <c r="D24" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A25">
+        <v>5022</v>
+      </c>
+      <c r="B25" t="s">
+        <v>41</v>
+      </c>
+      <c r="C25">
+        <v>61</v>
+      </c>
+      <c r="D25" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A26">
+        <v>5023</v>
+      </c>
+      <c r="B26" t="s">
+        <v>42</v>
+      </c>
+      <c r="C26">
+        <v>60</v>
+      </c>
+      <c r="D26" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <v>5024</v>
+      </c>
+      <c r="B27" t="s">
+        <v>44</v>
+      </c>
+      <c r="C27">
+        <v>53</v>
+      </c>
+      <c r="D27" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <v>5025</v>
+      </c>
+      <c r="B28" t="s">
+        <v>45</v>
+      </c>
+      <c r="C28">
+        <v>70</v>
+      </c>
+      <c r="D28" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <v>5026</v>
+      </c>
+      <c r="B29" t="s">
+        <v>46</v>
+      </c>
+      <c r="C29">
+        <v>69</v>
+      </c>
+      <c r="D29" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <v>5027</v>
+      </c>
+      <c r="B30" t="s">
+        <v>48</v>
+      </c>
+      <c r="C30">
+        <v>48</v>
+      </c>
+      <c r="D30" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A31">
+        <v>5028</v>
+      </c>
+      <c r="B31" t="s">
+        <v>49</v>
+      </c>
+      <c r="C31">
+        <v>52</v>
+      </c>
+      <c r="D31" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A32">
+        <v>5029</v>
+      </c>
+      <c r="B32" t="s">
+        <v>50</v>
+      </c>
+      <c r="C32">
+        <v>73</v>
+      </c>
+      <c r="D32" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A33">
+        <v>5030</v>
+      </c>
+      <c r="B33" t="s">
+        <v>51</v>
+      </c>
+      <c r="C33">
+        <v>71</v>
+      </c>
+      <c r="D33" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A34">
+        <v>5031</v>
+      </c>
+      <c r="B34" t="s">
+        <v>52</v>
+      </c>
+      <c r="C34">
+        <v>43</v>
+      </c>
+      <c r="D34" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A35">
+        <v>5032</v>
+      </c>
+      <c r="B35" t="s">
+        <v>53</v>
+      </c>
+      <c r="C35">
+        <v>42</v>
+      </c>
+      <c r="D35" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A36">
+        <v>5200</v>
+      </c>
+      <c r="B36" t="s">
+        <v>16</v>
+      </c>
+      <c r="C36" s="2">
+        <v>200</v>
+      </c>
+      <c r="D36" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A37">
+        <v>5201</v>
+      </c>
+      <c r="B37" t="s">
+        <v>20</v>
+      </c>
+      <c r="C37" s="2">
+        <v>201</v>
+      </c>
+      <c r="D37" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A38">
+        <v>5202</v>
+      </c>
+      <c r="B38" t="s">
+        <v>21</v>
+      </c>
+      <c r="C38" s="2">
+        <v>202</v>
+      </c>
+      <c r="D38" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A39">
+        <v>5203</v>
+      </c>
+      <c r="B39" t="s">
+        <v>22</v>
+      </c>
+      <c r="C39" s="2">
+        <v>203</v>
+      </c>
+      <c r="D39" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A40">
+        <v>5204</v>
+      </c>
+      <c r="B40" t="s">
+        <v>23</v>
+      </c>
+      <c r="C40" s="2">
+        <v>204</v>
+      </c>
+      <c r="D40" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A41">
+        <v>5205</v>
+      </c>
+      <c r="B41" t="s">
+        <v>24</v>
+      </c>
+      <c r="C41" s="2">
+        <v>205</v>
+      </c>
+      <c r="D41" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A42">
+        <v>5206</v>
+      </c>
+      <c r="B42" t="s">
+        <v>36</v>
+      </c>
+      <c r="C42" s="2">
+        <v>206</v>
+      </c>
+      <c r="D42" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A43">
+        <v>5207</v>
+      </c>
+      <c r="B43" t="s">
+        <v>37</v>
+      </c>
+      <c r="C43" s="2">
+        <v>207</v>
+      </c>
+      <c r="D43" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A44">
+        <v>5208</v>
+      </c>
+      <c r="B44" t="s">
+        <v>43</v>
+      </c>
+      <c r="C44" s="2">
+        <v>208</v>
+      </c>
+      <c r="D44" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A45">
+        <v>5209</v>
+      </c>
+      <c r="B45" t="s">
+        <v>47</v>
+      </c>
+      <c r="C45" s="2">
+        <v>209</v>
+      </c>
+      <c r="D45" t="s">
+        <v>54</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="C6:F25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="6" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C6">
+        <v>5003</v>
+      </c>
+      <c r="D6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6">
+        <f>C6</f>
+        <v>5003</v>
+      </c>
+    </row>
+    <row r="7" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C7">
+        <v>5006</v>
+      </c>
+      <c r="D7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7" t="str">
+        <f>F6&amp;","&amp;C7</f>
+        <v>5003,5006</v>
+      </c>
+    </row>
+    <row r="8" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C8">
+        <v>5007</v>
+      </c>
+      <c r="D8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F8" t="str">
+        <f t="shared" ref="F8:F25" si="0">F7&amp;","&amp;C8</f>
+        <v>5003,5006,5007</v>
+      </c>
+    </row>
+    <row r="9" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C9">
+        <v>5008</v>
+      </c>
+      <c r="D9" t="s">
+        <v>25</v>
+      </c>
+      <c r="F9" t="str">
+        <f t="shared" si="0"/>
+        <v>5003,5006,5007,5008</v>
+      </c>
+    </row>
+    <row r="10" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C10">
+        <v>5011</v>
+      </c>
+      <c r="D10" t="s">
+        <v>28</v>
+      </c>
+      <c r="F10" t="str">
+        <f t="shared" si="0"/>
+        <v>5003,5006,5007,5008,5011</v>
+      </c>
+    </row>
+    <row r="11" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C11">
+        <v>5012</v>
+      </c>
+      <c r="D11" t="s">
+        <v>29</v>
+      </c>
+      <c r="F11" t="str">
+        <f t="shared" si="0"/>
+        <v>5003,5006,5007,5008,5011,5012</v>
+      </c>
+    </row>
+    <row r="12" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C12">
+        <v>5013</v>
+      </c>
+      <c r="D12" t="s">
+        <v>30</v>
+      </c>
+      <c r="F12" t="str">
+        <f t="shared" si="0"/>
+        <v>5003,5006,5007,5008,5011,5012,5013</v>
+      </c>
+    </row>
+    <row r="13" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C13">
+        <v>5015</v>
+      </c>
+      <c r="D13" t="s">
+        <v>32</v>
+      </c>
+      <c r="F13" t="str">
+        <f t="shared" si="0"/>
+        <v>5003,5006,5007,5008,5011,5012,5013,5015</v>
+      </c>
+    </row>
+    <row r="14" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C14">
+        <v>5017</v>
+      </c>
+      <c r="D14" t="s">
+        <v>34</v>
+      </c>
+      <c r="F14" t="str">
+        <f t="shared" si="0"/>
+        <v>5003,5006,5007,5008,5011,5012,5013,5015,5017</v>
+      </c>
+    </row>
+    <row r="15" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C15">
+        <v>5018</v>
+      </c>
+      <c r="D15" t="s">
+        <v>35</v>
+      </c>
+      <c r="F15" t="str">
+        <f t="shared" si="0"/>
+        <v>5003,5006,5007,5008,5011,5012,5013,5015,5017,5018</v>
+      </c>
+    </row>
+    <row r="16" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C16">
+        <v>5019</v>
+      </c>
+      <c r="D16" t="s">
+        <v>38</v>
+      </c>
+      <c r="F16" t="str">
+        <f t="shared" si="0"/>
+        <v>5003,5006,5007,5008,5011,5012,5013,5015,5017,5018,5019</v>
+      </c>
+    </row>
+    <row r="17" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C17">
+        <v>5020</v>
+      </c>
+      <c r="D17" t="s">
+        <v>39</v>
+      </c>
+      <c r="F17" t="str">
+        <f t="shared" si="0"/>
+        <v>5003,5006,5007,5008,5011,5012,5013,5015,5017,5018,5019,5020</v>
+      </c>
+    </row>
+    <row r="18" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C18">
+        <v>5022</v>
+      </c>
+      <c r="D18" t="s">
+        <v>41</v>
+      </c>
+      <c r="F18" t="str">
+        <f t="shared" si="0"/>
+        <v>5003,5006,5007,5008,5011,5012,5013,5015,5017,5018,5019,5020,5022</v>
+      </c>
+    </row>
+    <row r="19" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C19">
+        <v>5024</v>
+      </c>
+      <c r="D19" t="s">
+        <v>44</v>
+      </c>
+      <c r="F19" t="str">
+        <f t="shared" si="0"/>
+        <v>5003,5006,5007,5008,5011,5012,5013,5015,5017,5018,5019,5020,5022,5024</v>
+      </c>
+    </row>
+    <row r="20" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C20">
+        <v>5025</v>
+      </c>
+      <c r="D20" t="s">
+        <v>45</v>
+      </c>
+      <c r="F20" t="str">
+        <f t="shared" si="0"/>
+        <v>5003,5006,5007,5008,5011,5012,5013,5015,5017,5018,5019,5020,5022,5024,5025</v>
+      </c>
+    </row>
+    <row r="21" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C21">
+        <v>5026</v>
+      </c>
+      <c r="D21" t="s">
+        <v>46</v>
+      </c>
+      <c r="F21" t="str">
+        <f t="shared" si="0"/>
+        <v>5003,5006,5007,5008,5011,5012,5013,5015,5017,5018,5019,5020,5022,5024,5025,5026</v>
+      </c>
+    </row>
+    <row r="22" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C22">
+        <v>5028</v>
+      </c>
+      <c r="D22" t="s">
+        <v>49</v>
+      </c>
+      <c r="F22" t="str">
+        <f t="shared" si="0"/>
+        <v>5003,5006,5007,5008,5011,5012,5013,5015,5017,5018,5019,5020,5022,5024,5025,5026,5028</v>
+      </c>
+    </row>
+    <row r="23" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C23">
+        <v>5029</v>
+      </c>
+      <c r="D23" t="s">
+        <v>50</v>
+      </c>
+      <c r="F23" t="str">
+        <f t="shared" si="0"/>
+        <v>5003,5006,5007,5008,5011,5012,5013,5015,5017,5018,5019,5020,5022,5024,5025,5026,5028,5029</v>
+      </c>
+    </row>
+    <row r="24" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C24">
+        <v>5030</v>
+      </c>
+      <c r="D24" t="s">
+        <v>51</v>
+      </c>
+      <c r="F24" t="str">
+        <f t="shared" si="0"/>
+        <v>5003,5006,5007,5008,5011,5012,5013,5015,5017,5018,5019,5020,5022,5024,5025,5026,5028,5029,5030</v>
+      </c>
+    </row>
+    <row r="25" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C25">
+        <v>5032</v>
+      </c>
+      <c r="D25" t="s">
+        <v>53</v>
+      </c>
+      <c r="F25" t="str">
+        <f t="shared" si="0"/>
+        <v>5003,5006,5007,5008,5011,5012,5013,5015,5017,5018,5019,5020,5022,5024,5025,5026,5028,5029,5030,5032</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Datas/TempCharacterData.xlsx
+++ b/Datas/TempCharacterData.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="64">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -197,6 +197,36 @@
   </si>
   <si>
     <t>街溜子</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>defaultEmote</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mapEmote</t>
+  </si>
+  <si>
+    <t>areaEmote</t>
+  </si>
+  <si>
+    <t>defaultTalk</t>
+  </si>
+  <si>
+    <t>mapTalk</t>
+  </si>
+  <si>
+    <t>areaTalk</t>
+  </si>
+  <si>
+    <t>IntIntDictionary</t>
+  </si>
+  <si>
+    <t>2012,20002|2003,20003|2004,20004|1100,20005|2001,20006|2002,20006|2012,20006</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -247,13 +277,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -535,25 +568,29 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:F45"/>
+  <dimension ref="A2:L45"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="3" width="14.125" customWidth="1"/>
-    <col min="4" max="4" width="15.75" customWidth="1"/>
-    <col min="5" max="6" width="12.75" customWidth="1"/>
+    <col min="1" max="3" width="14.125" style="3" customWidth="1"/>
+    <col min="4" max="4" width="15.75" style="3" customWidth="1"/>
+    <col min="5" max="6" width="12.75" style="3" customWidth="1"/>
+    <col min="7" max="7" width="11" style="3" customWidth="1"/>
+    <col min="8" max="8" width="18.75" style="3" customWidth="1"/>
+    <col min="9" max="12" width="35.25" style="3" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="3" t="s">
         <v>2</v>
       </c>
       <c r="E2" s="1" t="s">
@@ -562,613 +599,895 @@
       <c r="F2" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+      <c r="G2" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A4">
+      <c r="G3" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A4" s="3">
         <v>5001</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C4" s="2">
         <v>100</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A5">
+    <row r="5" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A5" s="3">
         <v>5002</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="3">
         <v>68</v>
       </c>
-      <c r="D5" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A6">
+      <c r="D5" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G5" s="3">
+        <v>20001</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A6" s="3">
         <v>5003</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="3">
         <v>51</v>
       </c>
-      <c r="D6" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A7">
+      <c r="D6" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G6" s="3">
+        <v>20001</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A7" s="3">
         <v>5004</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="3">
         <v>62</v>
       </c>
-      <c r="D7" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A8">
+      <c r="D7" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G7" s="3">
+        <v>20001</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A8" s="3">
         <v>5005</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="3">
         <v>45</v>
       </c>
-      <c r="D8" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A9">
+      <c r="D8" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G8" s="3">
+        <v>20001</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A9" s="3">
         <v>5006</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="3">
         <v>47</v>
       </c>
-      <c r="D9" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A10">
+      <c r="D9" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G9" s="3">
+        <v>20001</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A10" s="3">
         <v>5007</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="3">
         <v>46</v>
       </c>
-      <c r="D10" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A11">
+      <c r="D10" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G10" s="3">
+        <v>20001</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A11" s="3">
         <v>5008</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C11">
-        <v>63</v>
-      </c>
-      <c r="D11" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A12">
+      <c r="C11" s="3">
+        <v>63</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G11" s="3">
+        <v>20001</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A12" s="3">
         <v>5009</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="3">
         <v>65</v>
       </c>
-      <c r="D12" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A13">
+      <c r="D12" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G12" s="3">
+        <v>20001</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A13" s="3">
         <v>5010</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="3">
         <v>41</v>
       </c>
-      <c r="D13" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A14">
+      <c r="D13" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G13" s="3">
+        <v>20001</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A14" s="3">
         <v>5011</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="3">
         <v>44</v>
       </c>
-      <c r="D14" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A15">
+      <c r="D14" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G14" s="3">
+        <v>20001</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A15" s="3">
         <v>5012</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="3">
         <v>66</v>
       </c>
-      <c r="D15" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A16">
+      <c r="D15" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G15" s="3">
+        <v>20001</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A16" s="3">
         <v>5013</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="3">
         <v>67</v>
       </c>
-      <c r="D16" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A17">
+      <c r="D16" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G16" s="3">
+        <v>20001</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A17" s="3">
         <v>5014</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="3">
         <v>72</v>
       </c>
-      <c r="D17" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18">
+      <c r="D17" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G17" s="3">
+        <v>20001</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A18" s="3">
         <v>5015</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C18">
+      <c r="C18" s="3">
         <v>50</v>
       </c>
-      <c r="D18" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A19">
+      <c r="D18" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G18" s="3">
+        <v>20001</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A19" s="3">
         <v>5016</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C19">
+      <c r="C19" s="3">
         <v>59</v>
       </c>
-      <c r="D19" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A20">
+      <c r="D19" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G19" s="3">
+        <v>20001</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A20" s="3">
         <v>5017</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C20">
-        <v>54</v>
-      </c>
-      <c r="D20" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A21">
+      <c r="C20" s="3">
+        <v>54</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G20" s="3">
+        <v>20001</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A21" s="3">
         <v>5018</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C21">
+      <c r="C21" s="3">
         <v>58</v>
       </c>
-      <c r="D21" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A22">
+      <c r="D21" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G21" s="3">
+        <v>20001</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A22" s="3">
         <v>5019</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C22">
+      <c r="C22" s="3">
         <v>55</v>
       </c>
-      <c r="D22" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A23">
+      <c r="D22" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G22" s="3">
+        <v>20001</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A23" s="3">
         <v>5020</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C23">
+      <c r="C23" s="3">
         <v>57</v>
       </c>
-      <c r="D23" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A24">
+      <c r="D23" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G23" s="3">
+        <v>20001</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A24" s="3">
         <v>5021</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C24">
+      <c r="C24" s="3">
         <v>56</v>
       </c>
-      <c r="D24" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A25">
+      <c r="D24" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G24" s="3">
+        <v>20001</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A25" s="3">
         <v>5022</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C25">
+      <c r="C25" s="3">
         <v>61</v>
       </c>
-      <c r="D25" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A26">
+      <c r="D25" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G25" s="3">
+        <v>20001</v>
+      </c>
+      <c r="I25" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A26" s="3">
         <v>5023</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C26">
+      <c r="C26" s="3">
         <v>60</v>
       </c>
-      <c r="D26" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A27">
+      <c r="D26" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G26" s="3">
+        <v>20001</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A27" s="3">
         <v>5024</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C27">
+      <c r="C27" s="3">
         <v>53</v>
       </c>
-      <c r="D27" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A28">
+      <c r="D27" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G27" s="3">
+        <v>20001</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A28" s="3">
         <v>5025</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C28">
+      <c r="C28" s="3">
         <v>70</v>
       </c>
-      <c r="D28" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A29">
+      <c r="D28" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G28" s="3">
+        <v>20001</v>
+      </c>
+      <c r="I28" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A29" s="3">
         <v>5026</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C29">
+      <c r="C29" s="3">
         <v>69</v>
       </c>
-      <c r="D29" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A30">
+      <c r="D29" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G29" s="3">
+        <v>20001</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A30" s="3">
         <v>5027</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C30">
+      <c r="C30" s="3">
         <v>48</v>
       </c>
-      <c r="D30" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A31">
+      <c r="D30" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G30" s="3">
+        <v>20001</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A31" s="3">
         <v>5028</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C31">
+      <c r="C31" s="3">
         <v>52</v>
       </c>
-      <c r="D31" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A32">
+      <c r="D31" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G31" s="3">
+        <v>20001</v>
+      </c>
+      <c r="I31" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A32" s="3">
         <v>5029</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C32">
+      <c r="C32" s="3">
         <v>73</v>
       </c>
-      <c r="D32" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A33">
+      <c r="D32" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G32" s="3">
+        <v>20001</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A33" s="3">
         <v>5030</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C33">
+      <c r="C33" s="3">
         <v>71</v>
       </c>
-      <c r="D33" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A34">
+      <c r="D33" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G33" s="3">
+        <v>20001</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A34" s="3">
         <v>5031</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C34">
+      <c r="C34" s="3">
         <v>43</v>
       </c>
-      <c r="D34" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A35">
+      <c r="D34" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G34" s="3">
+        <v>20001</v>
+      </c>
+      <c r="I34" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A35" s="3">
         <v>5032</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C35">
+      <c r="C35" s="3">
         <v>42</v>
       </c>
-      <c r="D35" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A36">
+      <c r="D35" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G35" s="3">
+        <v>20001</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A36" s="3">
         <v>5200</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C36" s="2">
         <v>200</v>
       </c>
-      <c r="D36" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A37">
+      <c r="D36" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G36" s="3">
+        <v>20001</v>
+      </c>
+      <c r="I36" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A37" s="3">
         <v>5201</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C37" s="2">
         <v>201</v>
       </c>
-      <c r="D37" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A38">
+      <c r="D37" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G37" s="3">
+        <v>20001</v>
+      </c>
+      <c r="I37" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A38" s="3">
         <v>5202</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" s="3" t="s">
         <v>21</v>
       </c>
       <c r="C38" s="2">
         <v>202</v>
       </c>
-      <c r="D38" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A39">
+      <c r="D38" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G38" s="3">
+        <v>20001</v>
+      </c>
+      <c r="I38" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A39" s="3">
         <v>5203</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C39" s="2">
         <v>203</v>
       </c>
-      <c r="D39" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A40">
+      <c r="D39" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G39" s="3">
+        <v>20001</v>
+      </c>
+      <c r="I39" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A40" s="3">
         <v>5204</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" s="3" t="s">
         <v>23</v>
       </c>
       <c r="C40" s="2">
         <v>204</v>
       </c>
-      <c r="D40" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A41">
+      <c r="D40" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G40" s="3">
+        <v>20001</v>
+      </c>
+      <c r="I40" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A41" s="3">
         <v>5205</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B41" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C41" s="2">
         <v>205</v>
       </c>
-      <c r="D41" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A42">
+      <c r="D41" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G41" s="3">
+        <v>20001</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A42" s="3">
         <v>5206</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B42" s="3" t="s">
         <v>36</v>
       </c>
       <c r="C42" s="2">
         <v>206</v>
       </c>
-      <c r="D42" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A43">
+      <c r="D42" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G42" s="3">
+        <v>20001</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A43" s="3">
         <v>5207</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B43" s="3" t="s">
         <v>37</v>
       </c>
       <c r="C43" s="2">
         <v>207</v>
       </c>
-      <c r="D43" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A44">
+      <c r="D43" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G43" s="3">
+        <v>20001</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A44" s="3">
         <v>5208</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B44" s="3" t="s">
         <v>43</v>
       </c>
       <c r="C44" s="2">
         <v>208</v>
       </c>
-      <c r="D44" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A45">
+      <c r="D44" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G44" s="3">
+        <v>20001</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A45" s="3">
         <v>5209</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B45" s="3" t="s">
         <v>47</v>
       </c>
       <c r="C45" s="2">
         <v>209</v>
       </c>
-      <c r="D45" t="s">
-        <v>54</v>
+      <c r="D45" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G45" s="3">
+        <v>20001</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>63</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/TempCharacterData.xlsx
+++ b/Datas/TempCharacterData.xlsx
@@ -669,6 +669,12 @@
       <c r="D4" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="G4" s="3">
+        <v>20001</v>
+      </c>
+      <c r="J4" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="5" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
@@ -689,6 +695,9 @@
       <c r="I5" s="3" t="s">
         <v>63</v>
       </c>
+      <c r="J5" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="6" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A6" s="3">
@@ -709,6 +718,9 @@
       <c r="I6" s="3" t="s">
         <v>63</v>
       </c>
+      <c r="J6" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="7" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A7" s="3">
@@ -729,6 +741,9 @@
       <c r="I7" s="3" t="s">
         <v>63</v>
       </c>
+      <c r="J7" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="8" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A8" s="3">
@@ -749,6 +764,9 @@
       <c r="I8" s="3" t="s">
         <v>63</v>
       </c>
+      <c r="J8" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="9" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A9" s="3">
@@ -769,6 +787,9 @@
       <c r="I9" s="3" t="s">
         <v>63</v>
       </c>
+      <c r="J9" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="10" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A10" s="3">
@@ -789,6 +810,9 @@
       <c r="I10" s="3" t="s">
         <v>63</v>
       </c>
+      <c r="J10" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="11" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
@@ -809,6 +833,9 @@
       <c r="I11" s="3" t="s">
         <v>63</v>
       </c>
+      <c r="J11" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="12" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
@@ -829,6 +856,9 @@
       <c r="I12" s="3" t="s">
         <v>63</v>
       </c>
+      <c r="J12" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A13" s="3">
@@ -849,6 +879,9 @@
       <c r="I13" s="3" t="s">
         <v>63</v>
       </c>
+      <c r="J13" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="14" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A14" s="3">
@@ -869,6 +902,9 @@
       <c r="I14" s="3" t="s">
         <v>63</v>
       </c>
+      <c r="J14" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="15" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A15" s="3">
@@ -889,6 +925,9 @@
       <c r="I15" s="3" t="s">
         <v>63</v>
       </c>
+      <c r="J15" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="16" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A16" s="3">
@@ -909,8 +948,11 @@
       <c r="I16" s="3" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="17" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="J16" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A17" s="3">
         <v>5014</v>
       </c>
@@ -929,8 +971,11 @@
       <c r="I17" s="3" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="18" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="J17" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A18" s="3">
         <v>5015</v>
       </c>
@@ -949,8 +994,11 @@
       <c r="I18" s="3" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="19" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="J18" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A19" s="3">
         <v>5016</v>
       </c>
@@ -969,8 +1017,11 @@
       <c r="I19" s="3" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="20" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="J19" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A20" s="3">
         <v>5017</v>
       </c>
@@ -989,8 +1040,11 @@
       <c r="I20" s="3" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="21" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="J20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A21" s="3">
         <v>5018</v>
       </c>
@@ -1009,8 +1063,11 @@
       <c r="I21" s="3" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="22" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="J21" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A22" s="3">
         <v>5019</v>
       </c>
@@ -1029,8 +1086,11 @@
       <c r="I22" s="3" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="23" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="J22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A23" s="3">
         <v>5020</v>
       </c>
@@ -1049,8 +1109,11 @@
       <c r="I23" s="3" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="24" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="J23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A24" s="3">
         <v>5021</v>
       </c>
@@ -1069,8 +1132,11 @@
       <c r="I24" s="3" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="25" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="J24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A25" s="3">
         <v>5022</v>
       </c>
@@ -1089,8 +1155,11 @@
       <c r="I25" s="3" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="26" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="J25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A26" s="3">
         <v>5023</v>
       </c>
@@ -1109,8 +1178,11 @@
       <c r="I26" s="3" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="27" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="J26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A27" s="3">
         <v>5024</v>
       </c>
@@ -1129,8 +1201,11 @@
       <c r="I27" s="3" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="28" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="J27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A28" s="3">
         <v>5025</v>
       </c>
@@ -1149,8 +1224,11 @@
       <c r="I28" s="3" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="29" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="J28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A29" s="3">
         <v>5026</v>
       </c>
@@ -1169,8 +1247,11 @@
       <c r="I29" s="3" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="30" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="J29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A30" s="3">
         <v>5027</v>
       </c>
@@ -1189,8 +1270,11 @@
       <c r="I30" s="3" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="31" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="J30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A31" s="3">
         <v>5028</v>
       </c>
@@ -1209,8 +1293,11 @@
       <c r="I31" s="3" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="32" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="J31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A32" s="3">
         <v>5029</v>
       </c>
@@ -1229,8 +1316,11 @@
       <c r="I32" s="3" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="33" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="J32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A33" s="3">
         <v>5030</v>
       </c>
@@ -1249,8 +1339,11 @@
       <c r="I33" s="3" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="34" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="J33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A34" s="3">
         <v>5031</v>
       </c>
@@ -1269,8 +1362,11 @@
       <c r="I34" s="3" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="35" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="J34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A35" s="3">
         <v>5032</v>
       </c>
@@ -1289,8 +1385,11 @@
       <c r="I35" s="3" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="36" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="J35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A36" s="3">
         <v>5200</v>
       </c>
@@ -1309,8 +1408,11 @@
       <c r="I36" s="3" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="37" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="J36" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A37" s="3">
         <v>5201</v>
       </c>
@@ -1329,8 +1431,11 @@
       <c r="I37" s="3" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="38" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="J37" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A38" s="3">
         <v>5202</v>
       </c>
@@ -1349,8 +1454,11 @@
       <c r="I38" s="3" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="39" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="J38" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A39" s="3">
         <v>5203</v>
       </c>
@@ -1369,8 +1477,11 @@
       <c r="I39" s="3" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="40" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="J39" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A40" s="3">
         <v>5204</v>
       </c>
@@ -1389,8 +1500,11 @@
       <c r="I40" s="3" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="41" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="J40" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A41" s="3">
         <v>5205</v>
       </c>
@@ -1409,8 +1523,11 @@
       <c r="I41" s="3" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="42" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="J41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A42" s="3">
         <v>5206</v>
       </c>
@@ -1429,8 +1546,11 @@
       <c r="I42" s="3" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="43" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="J42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A43" s="3">
         <v>5207</v>
       </c>
@@ -1449,8 +1569,11 @@
       <c r="I43" s="3" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="44" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="J43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A44" s="3">
         <v>5208</v>
       </c>
@@ -1469,8 +1592,11 @@
       <c r="I44" s="3" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="45" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="J44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A45" s="3">
         <v>5209</v>
       </c>
@@ -1488,6 +1614,9 @@
       </c>
       <c r="I45" s="3" t="s">
         <v>63</v>
+      </c>
+      <c r="J45" s="3">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/TempCharacterData.xlsx
+++ b/Datas/TempCharacterData.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="64">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -57,10 +57,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>List&lt;int&gt;</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>List&lt;string&gt;</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -69,9 +65,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>默认消费者</t>
-  </si>
-  <si>
     <t>匪徒</t>
   </si>
   <si>
@@ -228,6 +221,14 @@
   <si>
     <t>2012,20002|2003,20003|2004,20004|1100,20005|2001,20006|2002,20006|2012,20006</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>547,30006</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>List&lt;int2&gt;</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -277,7 +278,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -286,6 +287,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -575,7 +579,7 @@
     <col min="4" max="4" width="15.75" style="3" customWidth="1"/>
     <col min="5" max="6" width="12.75" style="3" customWidth="1"/>
     <col min="7" max="7" width="11" style="3" customWidth="1"/>
-    <col min="8" max="8" width="18.75" style="3" customWidth="1"/>
+    <col min="8" max="8" width="18.75" style="4" customWidth="1"/>
     <col min="9" max="12" width="35.25" style="3" customWidth="1"/>
     <col min="13" max="16384" width="9" style="3"/>
   </cols>
@@ -594,28 +598,28 @@
         <v>2</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="G2" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>62</v>
+        <v>53</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>60</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
@@ -638,39 +642,45 @@
         <v>7</v>
       </c>
       <c r="G3" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="I3" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="J3" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="K3" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="L3" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="K3" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="4" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A4" s="3">
         <v>5001</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C4" s="2">
         <v>100</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>12</v>
+        <v>52</v>
       </c>
       <c r="G4" s="3">
         <v>20001</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>61</v>
       </c>
       <c r="J4" s="3">
         <v>0</v>
@@ -681,19 +691,22 @@
         <v>5002</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C5" s="3">
         <v>68</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G5" s="3">
         <v>20001</v>
       </c>
+      <c r="H5" s="4" t="s">
+        <v>62</v>
+      </c>
       <c r="I5" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="J5" s="3">
         <v>0</v>
@@ -704,19 +717,22 @@
         <v>5003</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C6" s="3">
         <v>51</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G6" s="3">
         <v>20001</v>
       </c>
+      <c r="H6" s="4" t="s">
+        <v>62</v>
+      </c>
       <c r="I6" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="J6" s="3">
         <v>0</v>
@@ -727,19 +743,22 @@
         <v>5004</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C7" s="3">
         <v>62</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G7" s="3">
         <v>20001</v>
       </c>
+      <c r="H7" s="4" t="s">
+        <v>62</v>
+      </c>
       <c r="I7" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="J7" s="3">
         <v>0</v>
@@ -750,19 +769,22 @@
         <v>5005</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C8" s="3">
         <v>45</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G8" s="3">
         <v>20001</v>
       </c>
+      <c r="H8" s="4" t="s">
+        <v>62</v>
+      </c>
       <c r="I8" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="J8" s="3">
         <v>0</v>
@@ -773,19 +795,22 @@
         <v>5006</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C9" s="3">
         <v>47</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G9" s="3">
         <v>20001</v>
       </c>
+      <c r="H9" s="4" t="s">
+        <v>62</v>
+      </c>
       <c r="I9" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="J9" s="3">
         <v>0</v>
@@ -796,19 +821,22 @@
         <v>5007</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C10" s="3">
         <v>46</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G10" s="3">
         <v>20001</v>
       </c>
+      <c r="H10" s="4" t="s">
+        <v>62</v>
+      </c>
       <c r="I10" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="J10" s="3">
         <v>0</v>
@@ -819,19 +847,22 @@
         <v>5008</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C11" s="3">
         <v>63</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G11" s="3">
         <v>20001</v>
       </c>
+      <c r="H11" s="4" t="s">
+        <v>62</v>
+      </c>
       <c r="I11" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="J11" s="3">
         <v>0</v>
@@ -842,19 +873,22 @@
         <v>5009</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C12" s="3">
         <v>65</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G12" s="3">
         <v>20001</v>
       </c>
+      <c r="H12" s="4" t="s">
+        <v>62</v>
+      </c>
       <c r="I12" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="J12" s="3">
         <v>0</v>
@@ -865,19 +899,22 @@
         <v>5010</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C13" s="3">
         <v>41</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G13" s="3">
         <v>20001</v>
       </c>
+      <c r="H13" s="4" t="s">
+        <v>62</v>
+      </c>
       <c r="I13" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="J13" s="3">
         <v>0</v>
@@ -888,19 +925,22 @@
         <v>5011</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C14" s="3">
         <v>44</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G14" s="3">
         <v>20001</v>
       </c>
+      <c r="H14" s="4" t="s">
+        <v>62</v>
+      </c>
       <c r="I14" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="J14" s="3">
         <v>0</v>
@@ -911,19 +951,22 @@
         <v>5012</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C15" s="3">
         <v>66</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G15" s="3">
         <v>20001</v>
       </c>
+      <c r="H15" s="4" t="s">
+        <v>62</v>
+      </c>
       <c r="I15" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="J15" s="3">
         <v>0</v>
@@ -934,19 +977,22 @@
         <v>5013</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C16" s="3">
         <v>67</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G16" s="3">
         <v>20001</v>
       </c>
+      <c r="H16" s="4" t="s">
+        <v>62</v>
+      </c>
       <c r="I16" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="J16" s="3">
         <v>0</v>
@@ -957,19 +1003,22 @@
         <v>5014</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C17" s="3">
         <v>72</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G17" s="3">
         <v>20001</v>
       </c>
+      <c r="H17" s="4" t="s">
+        <v>62</v>
+      </c>
       <c r="I17" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="J17" s="3">
         <v>0</v>
@@ -980,19 +1029,22 @@
         <v>5015</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C18" s="3">
         <v>50</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G18" s="3">
         <v>20001</v>
       </c>
+      <c r="H18" s="4" t="s">
+        <v>62</v>
+      </c>
       <c r="I18" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="J18" s="3">
         <v>0</v>
@@ -1003,19 +1055,22 @@
         <v>5016</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C19" s="3">
         <v>59</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G19" s="3">
         <v>20001</v>
       </c>
+      <c r="H19" s="4" t="s">
+        <v>62</v>
+      </c>
       <c r="I19" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="J19" s="3">
         <v>0</v>
@@ -1026,19 +1081,22 @@
         <v>5017</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C20" s="3">
         <v>54</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G20" s="3">
         <v>20001</v>
       </c>
+      <c r="H20" s="4" t="s">
+        <v>62</v>
+      </c>
       <c r="I20" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="J20" s="3">
         <v>0</v>
@@ -1049,19 +1107,22 @@
         <v>5018</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C21" s="3">
         <v>58</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G21" s="3">
         <v>20001</v>
       </c>
+      <c r="H21" s="4" t="s">
+        <v>62</v>
+      </c>
       <c r="I21" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="J21" s="3">
         <v>0</v>
@@ -1072,19 +1133,22 @@
         <v>5019</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C22" s="3">
         <v>55</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G22" s="3">
         <v>20001</v>
       </c>
+      <c r="H22" s="4" t="s">
+        <v>62</v>
+      </c>
       <c r="I22" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="J22" s="3">
         <v>0</v>
@@ -1095,19 +1159,22 @@
         <v>5020</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C23" s="3">
         <v>57</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G23" s="3">
         <v>20001</v>
       </c>
+      <c r="H23" s="4" t="s">
+        <v>62</v>
+      </c>
       <c r="I23" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="J23" s="3">
         <v>0</v>
@@ -1118,19 +1185,22 @@
         <v>5021</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C24" s="3">
         <v>56</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G24" s="3">
         <v>20001</v>
       </c>
+      <c r="H24" s="4" t="s">
+        <v>62</v>
+      </c>
       <c r="I24" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="J24" s="3">
         <v>0</v>
@@ -1141,19 +1211,22 @@
         <v>5022</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C25" s="3">
         <v>61</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G25" s="3">
         <v>20001</v>
       </c>
+      <c r="H25" s="4" t="s">
+        <v>62</v>
+      </c>
       <c r="I25" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="J25" s="3">
         <v>0</v>
@@ -1164,19 +1237,22 @@
         <v>5023</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C26" s="3">
         <v>60</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G26" s="3">
         <v>20001</v>
       </c>
+      <c r="H26" s="4" t="s">
+        <v>62</v>
+      </c>
       <c r="I26" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="J26" s="3">
         <v>0</v>
@@ -1187,19 +1263,22 @@
         <v>5024</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C27" s="3">
         <v>53</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G27" s="3">
         <v>20001</v>
       </c>
+      <c r="H27" s="4" t="s">
+        <v>62</v>
+      </c>
       <c r="I27" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="J27" s="3">
         <v>0</v>
@@ -1210,19 +1289,22 @@
         <v>5025</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C28" s="3">
         <v>70</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G28" s="3">
         <v>20001</v>
       </c>
+      <c r="H28" s="4" t="s">
+        <v>62</v>
+      </c>
       <c r="I28" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="J28" s="3">
         <v>0</v>
@@ -1233,19 +1315,22 @@
         <v>5026</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C29" s="3">
         <v>69</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G29" s="3">
         <v>20001</v>
       </c>
+      <c r="H29" s="4" t="s">
+        <v>62</v>
+      </c>
       <c r="I29" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="J29" s="3">
         <v>0</v>
@@ -1256,19 +1341,22 @@
         <v>5027</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C30" s="3">
         <v>48</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G30" s="3">
         <v>20001</v>
       </c>
+      <c r="H30" s="4" t="s">
+        <v>62</v>
+      </c>
       <c r="I30" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="J30" s="3">
         <v>0</v>
@@ -1279,19 +1367,22 @@
         <v>5028</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C31" s="3">
         <v>52</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G31" s="3">
         <v>20001</v>
       </c>
+      <c r="H31" s="4" t="s">
+        <v>62</v>
+      </c>
       <c r="I31" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="J31" s="3">
         <v>0</v>
@@ -1302,19 +1393,22 @@
         <v>5029</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C32" s="3">
         <v>73</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G32" s="3">
         <v>20001</v>
       </c>
+      <c r="H32" s="4" t="s">
+        <v>62</v>
+      </c>
       <c r="I32" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="J32" s="3">
         <v>0</v>
@@ -1325,19 +1419,22 @@
         <v>5030</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C33" s="3">
         <v>71</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G33" s="3">
         <v>20001</v>
       </c>
+      <c r="H33" s="4" t="s">
+        <v>62</v>
+      </c>
       <c r="I33" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="J33" s="3">
         <v>0</v>
@@ -1348,19 +1445,22 @@
         <v>5031</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C34" s="3">
         <v>43</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G34" s="3">
         <v>20001</v>
       </c>
+      <c r="H34" s="4" t="s">
+        <v>62</v>
+      </c>
       <c r="I34" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="J34" s="3">
         <v>0</v>
@@ -1371,19 +1471,22 @@
         <v>5032</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C35" s="3">
         <v>42</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G35" s="3">
         <v>20001</v>
       </c>
+      <c r="H35" s="4" t="s">
+        <v>62</v>
+      </c>
       <c r="I35" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="J35" s="3">
         <v>0</v>
@@ -1394,19 +1497,22 @@
         <v>5200</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C36" s="2">
         <v>200</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G36" s="3">
         <v>20001</v>
       </c>
+      <c r="H36" s="4" t="s">
+        <v>62</v>
+      </c>
       <c r="I36" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="J36" s="3">
         <v>0</v>
@@ -1417,19 +1523,22 @@
         <v>5201</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C37" s="2">
         <v>201</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G37" s="3">
         <v>20001</v>
       </c>
+      <c r="H37" s="4" t="s">
+        <v>62</v>
+      </c>
       <c r="I37" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="J37" s="3">
         <v>0</v>
@@ -1440,19 +1549,22 @@
         <v>5202</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C38" s="2">
         <v>202</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G38" s="3">
         <v>20001</v>
       </c>
+      <c r="H38" s="4" t="s">
+        <v>62</v>
+      </c>
       <c r="I38" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="J38" s="3">
         <v>0</v>
@@ -1463,19 +1575,22 @@
         <v>5203</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C39" s="2">
         <v>203</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G39" s="3">
         <v>20001</v>
       </c>
+      <c r="H39" s="4" t="s">
+        <v>62</v>
+      </c>
       <c r="I39" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="J39" s="3">
         <v>0</v>
@@ -1486,19 +1601,22 @@
         <v>5204</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C40" s="2">
         <v>204</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G40" s="3">
         <v>20001</v>
       </c>
+      <c r="H40" s="4" t="s">
+        <v>62</v>
+      </c>
       <c r="I40" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="J40" s="3">
         <v>0</v>
@@ -1509,19 +1627,22 @@
         <v>5205</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C41" s="2">
         <v>205</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G41" s="3">
         <v>20001</v>
       </c>
+      <c r="H41" s="4" t="s">
+        <v>62</v>
+      </c>
       <c r="I41" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="J41" s="3">
         <v>0</v>
@@ -1532,19 +1653,22 @@
         <v>5206</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C42" s="2">
         <v>206</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G42" s="3">
         <v>20001</v>
       </c>
+      <c r="H42" s="4" t="s">
+        <v>62</v>
+      </c>
       <c r="I42" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="J42" s="3">
         <v>0</v>
@@ -1555,19 +1679,22 @@
         <v>5207</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C43" s="2">
         <v>207</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G43" s="3">
         <v>20001</v>
       </c>
+      <c r="H43" s="4" t="s">
+        <v>62</v>
+      </c>
       <c r="I43" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="J43" s="3">
         <v>0</v>
@@ -1578,19 +1705,22 @@
         <v>5208</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C44" s="2">
         <v>208</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G44" s="3">
         <v>20001</v>
       </c>
+      <c r="H44" s="4" t="s">
+        <v>62</v>
+      </c>
       <c r="I44" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="J44" s="3">
         <v>0</v>
@@ -1601,19 +1731,22 @@
         <v>5209</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C45" s="2">
         <v>209</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G45" s="3">
         <v>20001</v>
       </c>
+      <c r="H45" s="4" t="s">
+        <v>62</v>
+      </c>
       <c r="I45" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="J45" s="3">
         <v>0</v>
@@ -1636,7 +1769,7 @@
         <v>5003</v>
       </c>
       <c r="D6" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F6">
         <f>C6</f>
@@ -1648,7 +1781,7 @@
         <v>5006</v>
       </c>
       <c r="D7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F7" t="str">
         <f>F6&amp;","&amp;C7</f>
@@ -1660,7 +1793,7 @@
         <v>5007</v>
       </c>
       <c r="D8" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F8" t="str">
         <f t="shared" ref="F8:F25" si="0">F7&amp;","&amp;C8</f>
@@ -1672,7 +1805,7 @@
         <v>5008</v>
       </c>
       <c r="D9" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F9" t="str">
         <f t="shared" si="0"/>
@@ -1684,7 +1817,7 @@
         <v>5011</v>
       </c>
       <c r="D10" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F10" t="str">
         <f t="shared" si="0"/>
@@ -1696,7 +1829,7 @@
         <v>5012</v>
       </c>
       <c r="D11" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F11" t="str">
         <f t="shared" si="0"/>
@@ -1708,7 +1841,7 @@
         <v>5013</v>
       </c>
       <c r="D12" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F12" t="str">
         <f t="shared" si="0"/>
@@ -1720,7 +1853,7 @@
         <v>5015</v>
       </c>
       <c r="D13" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F13" t="str">
         <f t="shared" si="0"/>
@@ -1732,7 +1865,7 @@
         <v>5017</v>
       </c>
       <c r="D14" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F14" t="str">
         <f t="shared" si="0"/>
@@ -1744,7 +1877,7 @@
         <v>5018</v>
       </c>
       <c r="D15" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F15" t="str">
         <f t="shared" si="0"/>
@@ -1756,7 +1889,7 @@
         <v>5019</v>
       </c>
       <c r="D16" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F16" t="str">
         <f t="shared" si="0"/>
@@ -1768,7 +1901,7 @@
         <v>5020</v>
       </c>
       <c r="D17" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F17" t="str">
         <f t="shared" si="0"/>
@@ -1780,7 +1913,7 @@
         <v>5022</v>
       </c>
       <c r="D18" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F18" t="str">
         <f t="shared" si="0"/>
@@ -1792,7 +1925,7 @@
         <v>5024</v>
       </c>
       <c r="D19" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F19" t="str">
         <f t="shared" si="0"/>
@@ -1804,7 +1937,7 @@
         <v>5025</v>
       </c>
       <c r="D20" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F20" t="str">
         <f t="shared" si="0"/>
@@ -1816,7 +1949,7 @@
         <v>5026</v>
       </c>
       <c r="D21" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F21" t="str">
         <f t="shared" si="0"/>
@@ -1828,7 +1961,7 @@
         <v>5028</v>
       </c>
       <c r="D22" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F22" t="str">
         <f t="shared" si="0"/>
@@ -1840,7 +1973,7 @@
         <v>5029</v>
       </c>
       <c r="D23" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F23" t="str">
         <f t="shared" si="0"/>
@@ -1852,7 +1985,7 @@
         <v>5030</v>
       </c>
       <c r="D24" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F24" t="str">
         <f t="shared" si="0"/>
@@ -1864,7 +1997,7 @@
         <v>5032</v>
       </c>
       <c r="D25" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F25" t="str">
         <f t="shared" si="0"/>

--- a/Datas/TempCharacterData.xlsx
+++ b/Datas/TempCharacterData.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="63">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -93,15 +93,6 @@
     <t>魔族法师</t>
   </si>
   <si>
-    <t>魔族娃娃</t>
-  </si>
-  <si>
-    <t>女鬼</t>
-  </si>
-  <si>
-    <t>女魔族</t>
-  </si>
-  <si>
     <t>女轻战士</t>
   </si>
   <si>
@@ -135,12 +126,6 @@
     <t>小混混</t>
   </si>
   <si>
-    <t>小精灵红</t>
-  </si>
-  <si>
-    <t>小精灵黄</t>
-  </si>
-  <si>
     <t>小美</t>
   </si>
   <si>
@@ -156,9 +141,6 @@
     <t>小女孩2</t>
   </si>
   <si>
-    <t>邪恶法师</t>
-  </si>
-  <si>
     <t>异国女子</t>
   </si>
   <si>
@@ -166,9 +148,6 @@
   </si>
   <si>
     <t>勇者女</t>
-  </si>
-  <si>
-    <t>幽灵战士</t>
   </si>
   <si>
     <t>游侠</t>
@@ -229,6 +208,30 @@
   <si>
     <t>List&lt;int2&gt;</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>路人女</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>路人男</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中年路人女</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中年路人男</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>红发小孩</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黄衣服小女孩</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -572,7 +575,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:L45"/>
+  <dimension ref="A2:L44"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="3" width="14.125" style="3" customWidth="1"/>
@@ -598,28 +601,28 @@
         <v>2</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>9</v>
       </c>
       <c r="G2" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="H2" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="H2" s="4" t="s">
-        <v>60</v>
-      </c>
       <c r="I2" s="3" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="J2" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="K2" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="K2" s="3" t="s">
-        <v>60</v>
-      </c>
       <c r="L2" s="3" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
@@ -642,22 +645,22 @@
         <v>7</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
@@ -671,16 +674,16 @@
         <v>100</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="G4" s="3">
         <v>20001</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="J4" s="3">
         <v>0</v>
@@ -697,16 +700,16 @@
         <v>68</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="G5" s="3">
         <v>20001</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="J5" s="3">
         <v>0</v>
@@ -723,16 +726,16 @@
         <v>51</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="G6" s="3">
         <v>20001</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="J6" s="3">
         <v>0</v>
@@ -749,16 +752,16 @@
         <v>62</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="G7" s="3">
         <v>20001</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="J7" s="3">
         <v>0</v>
@@ -775,16 +778,16 @@
         <v>45</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="G8" s="3">
         <v>20001</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="J8" s="3">
         <v>0</v>
@@ -801,16 +804,16 @@
         <v>47</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="G9" s="3">
         <v>20001</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="J9" s="3">
         <v>0</v>
@@ -827,16 +830,16 @@
         <v>46</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="G10" s="3">
         <v>20001</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="J10" s="3">
         <v>0</v>
@@ -847,22 +850,22 @@
         <v>5008</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C11" s="3">
         <v>63</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="G11" s="3">
         <v>20001</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="J11" s="3">
         <v>0</v>
@@ -873,22 +876,22 @@
         <v>5009</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C12" s="3">
         <v>65</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="G12" s="3">
         <v>20001</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="J12" s="3">
         <v>0</v>
@@ -899,22 +902,22 @@
         <v>5010</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C13" s="3">
         <v>41</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="G13" s="3">
         <v>20001</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="J13" s="3">
         <v>0</v>
@@ -925,22 +928,22 @@
         <v>5011</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C14" s="3">
         <v>44</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="G14" s="3">
         <v>20001</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="J14" s="3">
         <v>0</v>
@@ -951,22 +954,22 @@
         <v>5012</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C15" s="3">
         <v>66</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="G15" s="3">
         <v>20001</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="J15" s="3">
         <v>0</v>
@@ -977,22 +980,22 @@
         <v>5013</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C16" s="3">
         <v>67</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="G16" s="3">
         <v>20001</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="J16" s="3">
         <v>0</v>
@@ -1003,22 +1006,22 @@
         <v>5014</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C17" s="3">
         <v>72</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="G17" s="3">
         <v>20001</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="J17" s="3">
         <v>0</v>
@@ -1029,22 +1032,22 @@
         <v>5015</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C18" s="3">
         <v>50</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="G18" s="3">
         <v>20001</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="J18" s="3">
         <v>0</v>
@@ -1055,22 +1058,22 @@
         <v>5016</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C19" s="3">
         <v>59</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="G19" s="3">
         <v>20001</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="J19" s="3">
         <v>0</v>
@@ -1081,22 +1084,22 @@
         <v>5017</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C20" s="3">
         <v>54</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="G20" s="3">
         <v>20001</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="J20" s="3">
         <v>0</v>
@@ -1107,22 +1110,22 @@
         <v>5018</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C21" s="3">
         <v>58</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="G21" s="3">
         <v>20001</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="J21" s="3">
         <v>0</v>
@@ -1133,22 +1136,22 @@
         <v>5019</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="C22" s="3">
         <v>55</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="G22" s="3">
         <v>20001</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="J22" s="3">
         <v>0</v>
@@ -1159,22 +1162,22 @@
         <v>5020</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C23" s="3">
         <v>57</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="G23" s="3">
         <v>20001</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="J23" s="3">
         <v>0</v>
@@ -1185,22 +1188,22 @@
         <v>5021</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C24" s="3">
         <v>56</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="G24" s="3">
         <v>20001</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="J24" s="3">
         <v>0</v>
@@ -1211,22 +1214,22 @@
         <v>5022</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C25" s="3">
         <v>61</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="G25" s="3">
         <v>20001</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="J25" s="3">
         <v>0</v>
@@ -1237,22 +1240,22 @@
         <v>5023</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C26" s="3">
         <v>60</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="G26" s="3">
         <v>20001</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="J26" s="3">
         <v>0</v>
@@ -1263,22 +1266,22 @@
         <v>5024</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="C27" s="3">
         <v>53</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="G27" s="3">
         <v>20001</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="J27" s="3">
         <v>0</v>
@@ -1289,22 +1292,22 @@
         <v>5025</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C28" s="3">
         <v>70</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="G28" s="3">
         <v>20001</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="J28" s="3">
         <v>0</v>
@@ -1315,22 +1318,22 @@
         <v>5026</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="C29" s="3">
         <v>69</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="G29" s="3">
         <v>20001</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="J29" s="3">
         <v>0</v>
@@ -1341,22 +1344,22 @@
         <v>5027</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="C30" s="3">
         <v>48</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="G30" s="3">
         <v>20001</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="J30" s="3">
         <v>0</v>
@@ -1367,22 +1370,22 @@
         <v>5028</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="C31" s="3">
         <v>52</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="G31" s="3">
         <v>20001</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="J31" s="3">
         <v>0</v>
@@ -1393,22 +1396,22 @@
         <v>5029</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="C32" s="3">
         <v>73</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="G32" s="3">
         <v>20001</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="J32" s="3">
         <v>0</v>
@@ -1419,22 +1422,22 @@
         <v>5030</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="C33" s="3">
         <v>71</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="G33" s="3">
         <v>20001</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="J33" s="3">
         <v>0</v>
@@ -1445,22 +1448,22 @@
         <v>5031</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="C34" s="3">
         <v>43</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="G34" s="3">
         <v>20001</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="J34" s="3">
         <v>0</v>
@@ -1471,22 +1474,22 @@
         <v>5032</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="C35" s="3">
         <v>42</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="G35" s="3">
         <v>20001</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="J35" s="3">
         <v>0</v>
@@ -1503,16 +1506,16 @@
         <v>200</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="G36" s="3">
         <v>20001</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="J36" s="3">
         <v>0</v>
@@ -1529,16 +1532,16 @@
         <v>201</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="G37" s="3">
         <v>20001</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="J37" s="3">
         <v>0</v>
@@ -1555,16 +1558,16 @@
         <v>202</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="G38" s="3">
         <v>20001</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="J38" s="3">
         <v>0</v>
@@ -1575,22 +1578,22 @@
         <v>5203</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C39" s="2">
-        <v>203</v>
+        <v>59</v>
+      </c>
+      <c r="C39" s="3">
+        <v>210</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="G39" s="3">
         <v>20001</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="J39" s="3">
         <v>0</v>
@@ -1601,22 +1604,22 @@
         <v>5204</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C40" s="2">
-        <v>204</v>
+        <v>60</v>
+      </c>
+      <c r="C40" s="3">
+        <v>211</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="G40" s="3">
         <v>20001</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="J40" s="3">
         <v>0</v>
@@ -1627,22 +1630,22 @@
         <v>5205</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C41" s="2">
-        <v>205</v>
+        <v>61</v>
+      </c>
+      <c r="C41" s="3">
+        <v>212</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="G41" s="3">
         <v>20001</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="J41" s="3">
         <v>0</v>
@@ -1653,22 +1656,22 @@
         <v>5206</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C42" s="2">
-        <v>206</v>
+        <v>57</v>
+      </c>
+      <c r="C42" s="3">
+        <v>214</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="G42" s="3">
         <v>20001</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="J42" s="3">
         <v>0</v>
@@ -1679,22 +1682,22 @@
         <v>5207</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C43" s="2">
-        <v>207</v>
+        <v>58</v>
+      </c>
+      <c r="C43" s="3">
+        <v>215</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="G43" s="3">
         <v>20001</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="J43" s="3">
         <v>0</v>
@@ -1705,50 +1708,24 @@
         <v>5208</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C44" s="2">
-        <v>208</v>
+        <v>62</v>
+      </c>
+      <c r="C44" s="3">
+        <v>216</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="G44" s="3">
         <v>20001</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="J44" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A45" s="3">
-        <v>5209</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C45" s="2">
-        <v>209</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="G45" s="3">
-        <v>20001</v>
-      </c>
-      <c r="H45" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="J45" s="3">
         <v>0</v>
       </c>
     </row>
@@ -1805,7 +1782,7 @@
         <v>5008</v>
       </c>
       <c r="D9" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F9" t="str">
         <f t="shared" si="0"/>
@@ -1817,7 +1794,7 @@
         <v>5011</v>
       </c>
       <c r="D10" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F10" t="str">
         <f t="shared" si="0"/>
@@ -1829,7 +1806,7 @@
         <v>5012</v>
       </c>
       <c r="D11" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F11" t="str">
         <f t="shared" si="0"/>
@@ -1841,7 +1818,7 @@
         <v>5013</v>
       </c>
       <c r="D12" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F12" t="str">
         <f t="shared" si="0"/>
@@ -1853,7 +1830,7 @@
         <v>5015</v>
       </c>
       <c r="D13" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F13" t="str">
         <f t="shared" si="0"/>
@@ -1865,7 +1842,7 @@
         <v>5017</v>
       </c>
       <c r="D14" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F14" t="str">
         <f t="shared" si="0"/>
@@ -1877,7 +1854,7 @@
         <v>5018</v>
       </c>
       <c r="D15" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F15" t="str">
         <f t="shared" si="0"/>
@@ -1889,7 +1866,7 @@
         <v>5019</v>
       </c>
       <c r="D16" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F16" t="str">
         <f t="shared" si="0"/>
@@ -1901,7 +1878,7 @@
         <v>5020</v>
       </c>
       <c r="D17" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="F17" t="str">
         <f t="shared" si="0"/>
@@ -1913,7 +1890,7 @@
         <v>5022</v>
       </c>
       <c r="D18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="F18" t="str">
         <f t="shared" si="0"/>
@@ -1925,7 +1902,7 @@
         <v>5024</v>
       </c>
       <c r="D19" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F19" t="str">
         <f t="shared" si="0"/>
@@ -1937,7 +1914,7 @@
         <v>5025</v>
       </c>
       <c r="D20" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F20" t="str">
         <f t="shared" si="0"/>
@@ -1949,7 +1926,7 @@
         <v>5026</v>
       </c>
       <c r="D21" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="F21" t="str">
         <f t="shared" si="0"/>
@@ -1961,7 +1938,7 @@
         <v>5028</v>
       </c>
       <c r="D22" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="F22" t="str">
         <f t="shared" si="0"/>
@@ -1973,7 +1950,7 @@
         <v>5029</v>
       </c>
       <c r="D23" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="F23" t="str">
         <f t="shared" si="0"/>
@@ -1985,7 +1962,7 @@
         <v>5030</v>
       </c>
       <c r="D24" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="F24" t="str">
         <f t="shared" si="0"/>
@@ -1997,7 +1974,7 @@
         <v>5032</v>
       </c>
       <c r="D25" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="F25" t="str">
         <f t="shared" si="0"/>

--- a/Datas/TempCharacterData.xlsx
+++ b/Datas/TempCharacterData.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="67">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -232,6 +232,18 @@
   <si>
     <t>黄衣服小女孩</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>侍者</t>
+  </si>
+  <si>
+    <t>服务员</t>
+  </si>
+  <si>
+    <t>船员</t>
+  </si>
+  <si>
+    <t>贵族商人</t>
   </si>
 </sst>
 </file>
@@ -575,7 +587,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:L44"/>
+  <dimension ref="A2:L48"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="3" width="14.125" style="3" customWidth="1"/>
@@ -1726,6 +1738,110 @@
         <v>54</v>
       </c>
       <c r="J44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A45" s="3">
+        <v>5209</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C45" s="3">
+        <v>217</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G45" s="3">
+        <v>20001</v>
+      </c>
+      <c r="H45" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="J45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A46" s="3">
+        <v>5210</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C46" s="3">
+        <v>218</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G46" s="3">
+        <v>20001</v>
+      </c>
+      <c r="H46" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="J46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A47" s="3">
+        <v>5211</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C47" s="3">
+        <v>219</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G47" s="3">
+        <v>20001</v>
+      </c>
+      <c r="H47" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="J47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A48" s="3">
+        <v>5212</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C48" s="3">
+        <v>220</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G48" s="3">
+        <v>20001</v>
+      </c>
+      <c r="H48" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="J48" s="3">
         <v>0</v>
       </c>
     </row>

--- a/Datas/TempCharacterData.xlsx
+++ b/Datas/TempCharacterData.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="68">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -244,6 +244,10 @@
   </si>
   <si>
     <t>贵族商人</t>
+  </si>
+  <si>
+    <t>普通战士</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -940,7 +944,7 @@
         <v>5011</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>23</v>
+        <v>67</v>
       </c>
       <c r="C14" s="3">
         <v>44</v>

--- a/Datas/TempCharacterData.xlsx
+++ b/Datas/TempCharacterData.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="70">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -247,6 +247,14 @@
   </si>
   <si>
     <t>普通战士</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>消费者</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,547</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -692,6 +700,12 @@
       <c r="D4" s="3" t="s">
         <v>45</v>
       </c>
+      <c r="E4" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>68</v>
+      </c>
       <c r="G4" s="3">
         <v>20001</v>
       </c>
@@ -718,6 +732,12 @@
       <c r="D5" s="3" t="s">
         <v>45</v>
       </c>
+      <c r="E5" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>68</v>
+      </c>
       <c r="G5" s="3">
         <v>20001</v>
       </c>
@@ -744,6 +764,12 @@
       <c r="D6" s="3" t="s">
         <v>45</v>
       </c>
+      <c r="E6" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>68</v>
+      </c>
       <c r="G6" s="3">
         <v>20001</v>
       </c>
@@ -770,6 +796,12 @@
       <c r="D7" s="3" t="s">
         <v>45</v>
       </c>
+      <c r="E7" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>68</v>
+      </c>
       <c r="G7" s="3">
         <v>20001</v>
       </c>
@@ -796,6 +828,12 @@
       <c r="D8" s="3" t="s">
         <v>45</v>
       </c>
+      <c r="E8" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>68</v>
+      </c>
       <c r="G8" s="3">
         <v>20001</v>
       </c>
@@ -822,6 +860,12 @@
       <c r="D9" s="3" t="s">
         <v>45</v>
       </c>
+      <c r="E9" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>68</v>
+      </c>
       <c r="G9" s="3">
         <v>20001</v>
       </c>
@@ -848,6 +892,12 @@
       <c r="D10" s="3" t="s">
         <v>45</v>
       </c>
+      <c r="E10" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>68</v>
+      </c>
       <c r="G10" s="3">
         <v>20001</v>
       </c>
@@ -874,6 +924,12 @@
       <c r="D11" s="3" t="s">
         <v>45</v>
       </c>
+      <c r="E11" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>68</v>
+      </c>
       <c r="G11" s="3">
         <v>20001</v>
       </c>
@@ -900,6 +956,12 @@
       <c r="D12" s="3" t="s">
         <v>45</v>
       </c>
+      <c r="E12" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>68</v>
+      </c>
       <c r="G12" s="3">
         <v>20001</v>
       </c>
@@ -926,6 +988,12 @@
       <c r="D13" s="3" t="s">
         <v>45</v>
       </c>
+      <c r="E13" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>68</v>
+      </c>
       <c r="G13" s="3">
         <v>20001</v>
       </c>
@@ -952,6 +1020,12 @@
       <c r="D14" s="3" t="s">
         <v>45</v>
       </c>
+      <c r="E14" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>68</v>
+      </c>
       <c r="G14" s="3">
         <v>20001</v>
       </c>
@@ -978,6 +1052,12 @@
       <c r="D15" s="3" t="s">
         <v>45</v>
       </c>
+      <c r="E15" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>68</v>
+      </c>
       <c r="G15" s="3">
         <v>20001</v>
       </c>
@@ -1004,6 +1084,12 @@
       <c r="D16" s="3" t="s">
         <v>45</v>
       </c>
+      <c r="E16" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>68</v>
+      </c>
       <c r="G16" s="3">
         <v>20001</v>
       </c>
@@ -1030,6 +1116,12 @@
       <c r="D17" s="3" t="s">
         <v>45</v>
       </c>
+      <c r="E17" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>68</v>
+      </c>
       <c r="G17" s="3">
         <v>20001</v>
       </c>
@@ -1056,6 +1148,12 @@
       <c r="D18" s="3" t="s">
         <v>45</v>
       </c>
+      <c r="E18" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>68</v>
+      </c>
       <c r="G18" s="3">
         <v>20001</v>
       </c>
@@ -1082,6 +1180,12 @@
       <c r="D19" s="3" t="s">
         <v>45</v>
       </c>
+      <c r="E19" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>68</v>
+      </c>
       <c r="G19" s="3">
         <v>20001</v>
       </c>
@@ -1108,6 +1212,12 @@
       <c r="D20" s="3" t="s">
         <v>45</v>
       </c>
+      <c r="E20" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>68</v>
+      </c>
       <c r="G20" s="3">
         <v>20001</v>
       </c>
@@ -1134,6 +1244,12 @@
       <c r="D21" s="3" t="s">
         <v>45</v>
       </c>
+      <c r="E21" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>68</v>
+      </c>
       <c r="G21" s="3">
         <v>20001</v>
       </c>
@@ -1160,6 +1276,12 @@
       <c r="D22" s="3" t="s">
         <v>45</v>
       </c>
+      <c r="E22" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>68</v>
+      </c>
       <c r="G22" s="3">
         <v>20001</v>
       </c>
@@ -1186,6 +1308,12 @@
       <c r="D23" s="3" t="s">
         <v>45</v>
       </c>
+      <c r="E23" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>68</v>
+      </c>
       <c r="G23" s="3">
         <v>20001</v>
       </c>
@@ -1212,6 +1340,12 @@
       <c r="D24" s="3" t="s">
         <v>45</v>
       </c>
+      <c r="E24" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>68</v>
+      </c>
       <c r="G24" s="3">
         <v>20001</v>
       </c>
@@ -1238,6 +1372,12 @@
       <c r="D25" s="3" t="s">
         <v>45</v>
       </c>
+      <c r="E25" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>68</v>
+      </c>
       <c r="G25" s="3">
         <v>20001</v>
       </c>
@@ -1264,6 +1404,12 @@
       <c r="D26" s="3" t="s">
         <v>45</v>
       </c>
+      <c r="E26" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>68</v>
+      </c>
       <c r="G26" s="3">
         <v>20001</v>
       </c>
@@ -1290,6 +1436,12 @@
       <c r="D27" s="3" t="s">
         <v>45</v>
       </c>
+      <c r="E27" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>68</v>
+      </c>
       <c r="G27" s="3">
         <v>20001</v>
       </c>
@@ -1316,6 +1468,12 @@
       <c r="D28" s="3" t="s">
         <v>45</v>
       </c>
+      <c r="E28" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>68</v>
+      </c>
       <c r="G28" s="3">
         <v>20001</v>
       </c>
@@ -1342,6 +1500,12 @@
       <c r="D29" s="3" t="s">
         <v>45</v>
       </c>
+      <c r="E29" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>68</v>
+      </c>
       <c r="G29" s="3">
         <v>20001</v>
       </c>
@@ -1368,6 +1532,12 @@
       <c r="D30" s="3" t="s">
         <v>45</v>
       </c>
+      <c r="E30" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>68</v>
+      </c>
       <c r="G30" s="3">
         <v>20001</v>
       </c>
@@ -1394,6 +1564,12 @@
       <c r="D31" s="3" t="s">
         <v>45</v>
       </c>
+      <c r="E31" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>68</v>
+      </c>
       <c r="G31" s="3">
         <v>20001</v>
       </c>
@@ -1420,6 +1596,12 @@
       <c r="D32" s="3" t="s">
         <v>45</v>
       </c>
+      <c r="E32" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>68</v>
+      </c>
       <c r="G32" s="3">
         <v>20001</v>
       </c>
@@ -1446,6 +1628,12 @@
       <c r="D33" s="3" t="s">
         <v>45</v>
       </c>
+      <c r="E33" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>68</v>
+      </c>
       <c r="G33" s="3">
         <v>20001</v>
       </c>
@@ -1472,6 +1660,12 @@
       <c r="D34" s="3" t="s">
         <v>45</v>
       </c>
+      <c r="E34" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>68</v>
+      </c>
       <c r="G34" s="3">
         <v>20001</v>
       </c>
@@ -1498,6 +1692,12 @@
       <c r="D35" s="3" t="s">
         <v>45</v>
       </c>
+      <c r="E35" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>68</v>
+      </c>
       <c r="G35" s="3">
         <v>20001</v>
       </c>
@@ -1524,6 +1724,12 @@
       <c r="D36" s="3" t="s">
         <v>45</v>
       </c>
+      <c r="E36" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>68</v>
+      </c>
       <c r="G36" s="3">
         <v>20001</v>
       </c>
@@ -1550,6 +1756,12 @@
       <c r="D37" s="3" t="s">
         <v>45</v>
       </c>
+      <c r="E37" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>68</v>
+      </c>
       <c r="G37" s="3">
         <v>20001</v>
       </c>
@@ -1576,6 +1788,12 @@
       <c r="D38" s="3" t="s">
         <v>45</v>
       </c>
+      <c r="E38" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>68</v>
+      </c>
       <c r="G38" s="3">
         <v>20001</v>
       </c>
@@ -1602,6 +1820,12 @@
       <c r="D39" s="3" t="s">
         <v>45</v>
       </c>
+      <c r="E39" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>68</v>
+      </c>
       <c r="G39" s="3">
         <v>20001</v>
       </c>
@@ -1628,6 +1852,12 @@
       <c r="D40" s="3" t="s">
         <v>45</v>
       </c>
+      <c r="E40" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>68</v>
+      </c>
       <c r="G40" s="3">
         <v>20001</v>
       </c>
@@ -1654,6 +1884,12 @@
       <c r="D41" s="3" t="s">
         <v>45</v>
       </c>
+      <c r="E41" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>68</v>
+      </c>
       <c r="G41" s="3">
         <v>20001</v>
       </c>
@@ -1680,6 +1916,12 @@
       <c r="D42" s="3" t="s">
         <v>45</v>
       </c>
+      <c r="E42" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>68</v>
+      </c>
       <c r="G42" s="3">
         <v>20001</v>
       </c>
@@ -1706,6 +1948,12 @@
       <c r="D43" s="3" t="s">
         <v>45</v>
       </c>
+      <c r="E43" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>68</v>
+      </c>
       <c r="G43" s="3">
         <v>20001</v>
       </c>
@@ -1732,6 +1980,12 @@
       <c r="D44" s="3" t="s">
         <v>45</v>
       </c>
+      <c r="E44" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>68</v>
+      </c>
       <c r="G44" s="3">
         <v>20001</v>
       </c>
@@ -1758,6 +2012,12 @@
       <c r="D45" s="3" t="s">
         <v>45</v>
       </c>
+      <c r="E45" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>68</v>
+      </c>
       <c r="G45" s="3">
         <v>20001</v>
       </c>
@@ -1784,6 +2044,12 @@
       <c r="D46" s="3" t="s">
         <v>45</v>
       </c>
+      <c r="E46" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>68</v>
+      </c>
       <c r="G46" s="3">
         <v>20001</v>
       </c>
@@ -1810,6 +2076,12 @@
       <c r="D47" s="3" t="s">
         <v>45</v>
       </c>
+      <c r="E47" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>68</v>
+      </c>
       <c r="G47" s="3">
         <v>20001</v>
       </c>
@@ -1835,6 +2107,12 @@
       </c>
       <c r="D48" s="3" t="s">
         <v>45</v>
+      </c>
+      <c r="E48" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>68</v>
       </c>
       <c r="G48" s="3">
         <v>20001</v>

--- a/Datas/TempCharacterData.xlsx
+++ b/Datas/TempCharacterData.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="77">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -256,6 +256,33 @@
   <si>
     <t>1,547</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>教堂中年路人女</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>教堂中年路人男</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>教堂路人女</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>教堂黄衣服小女孩</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>教堂小男孩</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>教堂小男孩2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>教堂教徒</t>
   </si>
 </sst>
 </file>
@@ -599,7 +626,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:L48"/>
+  <dimension ref="A2:L54"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="3" width="14.125" style="3" customWidth="1"/>
@@ -2124,6 +2151,192 @@
         <v>54</v>
       </c>
       <c r="J48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A49" s="3">
+        <v>6000</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C49" s="3">
+        <v>210</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E49" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="G49" s="3">
+        <v>20001</v>
+      </c>
+      <c r="H49" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="J49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A50" s="3">
+        <v>6001</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C50" s="3">
+        <v>211</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E50" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="G50" s="3">
+        <v>20001</v>
+      </c>
+      <c r="H50" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="I50" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="J50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A51" s="3">
+        <v>6002</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C51" s="3">
+        <v>214</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E51" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="G51" s="3">
+        <v>20001</v>
+      </c>
+      <c r="H51" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="I51" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="J51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A52" s="3">
+        <v>6003</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C52" s="3">
+        <v>216</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E52" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="G52" s="3">
+        <v>20001</v>
+      </c>
+      <c r="H52" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="J52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A53" s="3">
+        <v>6004</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C53" s="3">
+        <v>57</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E53" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="G53" s="3">
+        <v>20001</v>
+      </c>
+      <c r="H53" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="I53" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="J53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A54" s="3">
+        <v>6005</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C54" s="3">
+        <v>56</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E54" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="G54" s="3">
+        <v>20001</v>
+      </c>
+      <c r="J54" s="3">
         <v>0</v>
       </c>
     </row>

--- a/Datas/TempCharacterData.xlsx
+++ b/Datas/TempCharacterData.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="59">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -163,14 +163,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>消费者</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1,547</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>男孩路人</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -221,6 +213,22 @@
   <si>
     <t>侍者女</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>消费者,教堂教徒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,547|1,3115</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,547|1,3115</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,547|1,3115|1,2180</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -567,13 +575,16 @@
   <dimension ref="A2:L16"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="3" width="14.125" style="3" customWidth="1"/>
+    <col min="1" max="2" width="14.125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="12.375" style="3" customWidth="1"/>
     <col min="4" max="4" width="15.75" style="3" customWidth="1"/>
-    <col min="5" max="6" width="12.75" style="3" customWidth="1"/>
+    <col min="5" max="5" width="18.875" style="3" customWidth="1"/>
+    <col min="6" max="6" width="17.5" style="3" customWidth="1"/>
     <col min="7" max="7" width="11" style="3" customWidth="1"/>
     <col min="8" max="8" width="18.75" style="4" customWidth="1"/>
     <col min="9" max="9" width="56.875" style="3" customWidth="1"/>
-    <col min="10" max="12" width="35.25" style="3" customWidth="1"/>
+    <col min="10" max="10" width="12.75" style="3" customWidth="1"/>
+    <col min="11" max="12" width="17.5" style="3" customWidth="1"/>
     <col min="13" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
@@ -658,7 +669,7 @@
         <v>5001</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C4" s="2">
         <v>50</v>
@@ -667,10 +678,10 @@
         <v>30</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="G4" s="3">
         <v>20001</v>
@@ -690,7 +701,7 @@
         <v>5002</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C5" s="2">
         <v>51</v>
@@ -699,10 +710,10 @@
         <v>30</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="G5" s="3">
         <v>20001</v>
@@ -722,7 +733,7 @@
         <v>5003</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C6" s="2">
         <v>52</v>
@@ -731,10 +742,10 @@
         <v>30</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="G6" s="3">
         <v>20001</v>
@@ -754,7 +765,7 @@
         <v>5004</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C7" s="2">
         <v>53</v>
@@ -763,10 +774,10 @@
         <v>30</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="G7" s="3">
         <v>20001</v>
@@ -786,7 +797,7 @@
         <v>5005</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C8" s="2">
         <v>54</v>
@@ -795,10 +806,10 @@
         <v>30</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="G8" s="3">
         <v>20001</v>
@@ -818,7 +829,7 @@
         <v>5006</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C9" s="2">
         <v>55</v>
@@ -827,10 +838,10 @@
         <v>30</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="G9" s="3">
         <v>20001</v>
@@ -850,7 +861,7 @@
         <v>5007</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C10" s="2">
         <v>56</v>
@@ -859,10 +870,10 @@
         <v>30</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="G10" s="3">
         <v>20001</v>
@@ -882,7 +893,7 @@
         <v>5008</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C11" s="2">
         <v>57</v>
@@ -891,10 +902,10 @@
         <v>30</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="G11" s="3">
         <v>20001</v>
@@ -914,7 +925,7 @@
         <v>5009</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C12" s="2">
         <v>58</v>
@@ -923,10 +934,10 @@
         <v>30</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="G12" s="3">
         <v>20001</v>
@@ -946,7 +957,7 @@
         <v>5010</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C13" s="2">
         <v>59</v>
@@ -955,10 +966,10 @@
         <v>30</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="G13" s="3">
         <v>20001</v>
@@ -978,7 +989,7 @@
         <v>5011</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C14" s="2">
         <v>60</v>
@@ -987,10 +998,10 @@
         <v>30</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="G14" s="3">
         <v>20001</v>
@@ -1010,7 +1021,7 @@
         <v>5012</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C15" s="2">
         <v>61</v>
@@ -1019,10 +1030,10 @@
         <v>30</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="G15" s="3">
         <v>20001</v>
@@ -1042,7 +1053,7 @@
         <v>5013</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C16" s="2">
         <v>62</v>
@@ -1051,10 +1062,10 @@
         <v>30</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="G16" s="3">
         <v>20001</v>

--- a/Datas/TempCharacterData.xlsx
+++ b/Datas/TempCharacterData.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="62">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -228,6 +228,18 @@
   </si>
   <si>
     <t>1,547|1,3115|1,2180</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>消费者,教堂教徒,酒馆客人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>547,30006</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>547,30006|2180,20007</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -687,7 +699,7 @@
         <v>20001</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>39</v>
@@ -745,13 +757,13 @@
         <v>58</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G6" s="3">
         <v>20001</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="I6" s="3" t="s">
         <v>39</v>
@@ -777,13 +789,13 @@
         <v>58</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G7" s="3">
         <v>20001</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="I7" s="3" t="s">
         <v>39</v>
@@ -809,13 +821,13 @@
         <v>58</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G8" s="3">
         <v>20001</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>39</v>
@@ -841,13 +853,13 @@
         <v>58</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G9" s="3">
         <v>20001</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>39</v>
@@ -873,13 +885,13 @@
         <v>58</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G10" s="3">
         <v>20001</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>39</v>
@@ -905,13 +917,13 @@
         <v>58</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G11" s="3">
         <v>20001</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="I11" s="3" t="s">
         <v>39</v>
@@ -937,13 +949,13 @@
         <v>58</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G12" s="3">
         <v>20001</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>39</v>
@@ -969,13 +981,13 @@
         <v>58</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G13" s="3">
         <v>20001</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="I13" s="3" t="s">
         <v>39</v>
@@ -1001,13 +1013,13 @@
         <v>58</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G14" s="3">
         <v>20001</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>39</v>
@@ -1033,13 +1045,13 @@
         <v>58</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G15" s="3">
         <v>20001</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="I15" s="3" t="s">
         <v>39</v>
@@ -1065,13 +1077,13 @@
         <v>58</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G16" s="3">
         <v>20001</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="I16" s="3" t="s">
         <v>39</v>

--- a/Datas/TempCharacterData.xlsx
+++ b/Datas/TempCharacterData.xlsx
@@ -215,10 +215,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>消费者,教堂教徒</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1,547|1,3115</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -231,16 +227,18 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>消费者,教堂教徒,酒馆客人</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>547,30006</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>547,30006|2180,20007</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>消费者|教堂教徒</t>
+  </si>
+  <si>
+    <t>消费者|教堂教徒|酒馆客人</t>
   </si>
 </sst>
 </file>
@@ -690,16 +688,16 @@
         <v>30</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="G4" s="3">
         <v>20001</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>39</v>
@@ -722,10 +720,10 @@
         <v>30</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="G5" s="3">
         <v>20001</v>
@@ -754,16 +752,16 @@
         <v>30</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G6" s="3">
         <v>20001</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I6" s="3" t="s">
         <v>39</v>
@@ -786,16 +784,16 @@
         <v>30</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G7" s="3">
         <v>20001</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I7" s="3" t="s">
         <v>39</v>
@@ -818,16 +816,16 @@
         <v>30</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G8" s="3">
         <v>20001</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>39</v>
@@ -850,16 +848,16 @@
         <v>30</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G9" s="3">
         <v>20001</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>39</v>
@@ -882,16 +880,16 @@
         <v>30</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G10" s="3">
         <v>20001</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>39</v>
@@ -914,16 +912,16 @@
         <v>30</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G11" s="3">
         <v>20001</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I11" s="3" t="s">
         <v>39</v>
@@ -946,16 +944,16 @@
         <v>30</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G12" s="3">
         <v>20001</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>39</v>
@@ -978,16 +976,16 @@
         <v>30</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G13" s="3">
         <v>20001</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I13" s="3" t="s">
         <v>39</v>
@@ -1010,16 +1008,16 @@
         <v>30</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G14" s="3">
         <v>20001</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>39</v>
@@ -1042,16 +1040,16 @@
         <v>30</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G15" s="3">
         <v>20001</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I15" s="3" t="s">
         <v>39</v>
@@ -1074,16 +1072,16 @@
         <v>30</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G16" s="3">
         <v>20001</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I16" s="3" t="s">
         <v>39</v>
